--- a/Test/TestCase_UAT.xlsx
+++ b/Test/TestCase_UAT.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\OneDrive\Desktop\online-movie-ticket-booking\Test\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B2D4EA-9954-43C0-9886-3804213FA07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="UAT Test Cases" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="UAT Test Cases" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -22,125 +30,122 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
   <si>
-    <t xml:space="preserve">Test ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Objective</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Related User Story</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Steps / Input</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actual Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tested By</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm a first-time customer can book a ticket without assistance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-01–US-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New user (non-technical) is asked to register and book one ticket unaided, task is timed and observed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User completes booking within 5 minutes without external help and rates experience 4/5 or higher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User completed booking in 4 minutes and rated experience 5/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salina Tiwari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm admin can update a showtime and see the change reflected to customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin changes a showtime from 6:00 PM to 7:30 PM; customer refreshes movie listing page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Updated showtime (7:30 PM) is visible to customers within 1 minute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Updated time appeared immediately on refresh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm cancellation and refund process meets customer expectations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer cancels a booking 3 hours before showtime and checks refund status page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer sees clear refund status and expected refund timeframe (3–5 business days)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refund status page did not display timeframe (related to TC-06 bug)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Cases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Failed</t>
+    <t>Test ID</t>
+  </si>
+  <si>
+    <t>Test Type</t>
+  </si>
+  <si>
+    <t>Test Objective</t>
+  </si>
+  <si>
+    <t>Related User Story</t>
+  </si>
+  <si>
+    <t>Test Steps / Input</t>
+  </si>
+  <si>
+    <t>Expected Output</t>
+  </si>
+  <si>
+    <t>Actual Output</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Tested By</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>TC-10</t>
+  </si>
+  <si>
+    <t>UAT</t>
+  </si>
+  <si>
+    <t>Confirm a first-time customer can book a ticket without assistance</t>
+  </si>
+  <si>
+    <t>US-01–US-04</t>
+  </si>
+  <si>
+    <t>New user (non-technical) is asked to register and book one ticket unaided, task is timed and observed</t>
+  </si>
+  <si>
+    <t>User completes booking within 5 minutes without external help and rates experience 4/5 or higher</t>
+  </si>
+  <si>
+    <t>User completed booking in 4 minutes and rated experience 5/5</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Salina Tiwari</t>
+  </si>
+  <si>
+    <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>TC-11</t>
+  </si>
+  <si>
+    <t>US-10</t>
+  </si>
+  <si>
+    <t>Admin changes a showtime from 6:00 PM to 7:30 PM; customer refreshes movie listing page</t>
+  </si>
+  <si>
+    <t>Updated showtime (7:30 PM) is visible to customers within 1 minute</t>
+  </si>
+  <si>
+    <t>Updated time appeared immediately on refresh</t>
+  </si>
+  <si>
+    <t>TC-12</t>
+  </si>
+  <si>
+    <t>Confirm cancellation and refund process meets customer expectations</t>
+  </si>
+  <si>
+    <t>US-05</t>
+  </si>
+  <si>
+    <t>Customer cancels a booking 3 hours before showtime and checks refund status page</t>
+  </si>
+  <si>
+    <t>Customer sees clear refund status and expected refund timeframe (3–5 business days)</t>
+  </si>
+  <si>
+    <t>Refund status page did not display timeframe (related to TC-06 bug)</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Total Cases</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Confirmm admin can update a showtime and see the change reflected to customers</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,39 +154,21 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -212,14 +199,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFB7B7B7"/>
       </left>
@@ -235,77 +222,33 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -364,47 +307,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1F4E78"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -412,12 +371,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -446,7 +405,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -467,7 +426,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -518,7 +477,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -536,34 +495,33 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
+    <col min="1" max="1" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -595,7 +553,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:10" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -627,7 +585,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:10" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -635,19 +593,19 @@
         <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>17</v>
@@ -659,30 +617,30 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:10" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>18</v>
@@ -691,42 +649,37 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="B7" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="B8" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="8">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>